--- a/仕様書ほか.xlsx
+++ b/仕様書ほか.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\katoy\i2c_use_memory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B02486-020F-4691-8974-CFB813D4EBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB4C83B-39C5-4CF6-9C4C-5FA6C3F8A528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="9915" activeTab="1" xr2:uid="{F144D80B-630C-43F9-9D23-4AE66E7F3353}"/>
+    <workbookView xWindow="43455" yWindow="0" windowWidth="14250" windowHeight="8205" activeTab="1" xr2:uid="{F144D80B-630C-43F9-9D23-4AE66E7F3353}"/>
   </bookViews>
   <sheets>
     <sheet name="仕様書" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="67">
   <si>
     <t>1, 概要</t>
     <rPh sb="3" eb="5">
@@ -267,10 +267,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>パラメータが規定より多いこと。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>データは16進数であるため、0-9, a-f,A-Fしか使えないこと。</t>
     <rPh sb="6" eb="8">
       <t>シンスウ</t>
@@ -371,6 +367,299 @@
     </rPh>
     <rPh sb="6" eb="8">
       <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全てのデータをアドレス順に表示する。</t>
+    <rPh sb="0" eb="1">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アドレス最大値定義（for文用、16進数）</t>
+    <rPh sb="4" eb="7">
+      <t>サイダイチ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>引数が無い場合全表示する。</t>
+    <rPh sb="0" eb="2">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ゼンヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>引数が規定より多いこと。</t>
+    <rPh sb="0" eb="2">
+      <t>ヒキスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データ全表示関数</t>
+  </si>
+  <si>
+    <t>parを桁ごとに分解する</t>
+    <rPh sb="4" eb="5">
+      <t>ケタ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ブンカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上記の結果をすべて足す</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>16進数一桁分変換関数</t>
+  </si>
+  <si>
+    <t>ローカルで引数を定義する</t>
+    <rPh sb="5" eb="7">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ローカルで引数を定義する。</t>
+    <rPh sb="5" eb="7">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>桁ごとに16の乗数を掛け算する</t>
+    <rPh sb="0" eb="1">
+      <t>ケタ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウスウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ザン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>for文で、parが0～15のとき、0～Fをechoするようにする。</t>
+    <rPh sb="3" eb="4">
+      <t>ブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>for文で、parがA～Fのとき、10～15をechoするようにする。</t>
+    <rPh sb="3" eb="4">
+      <t>ブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2桁の16進数を10進数に変える関数定義（while文用）</t>
+    <rPh sb="16" eb="18">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ブンヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>255までの10進数を16進数に変える関数定義（while文用）</t>
+    <rPh sb="19" eb="21">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データ全表示関数（while文）</t>
+    <rPh sb="3" eb="6">
+      <t>ゼンヒョウジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>16進数一桁分変換関数</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2桁の16進数を10進数に変換する関数</t>
+    <rPh sb="1" eb="2">
+      <t>ケタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>255までの10進数を16進数に変換する関数</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>16で剰余を出し、0乗目の値として変数に定義する。</t>
+    <rPh sb="3" eb="5">
+      <t>ジョウヨ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>16で商を出し、1乗目の値として変数に定義する。</t>
+    <rPh sb="3" eb="4">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジョウメ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商・あまりの順で並べて表示する。</t>
+    <rPh sb="0" eb="1">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ナラ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>指定した最終アドレスを10進数に変換し、while文を回す</t>
+    <rPh sb="0" eb="2">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サイシュウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シンスウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヘンカン</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>マワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カウントアップさせた値を16進数に戻してi2cgetをする</t>
+    <rPh sb="10" eb="11">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シンスウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>モド</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -759,7 +1048,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBAE3C68-FE4B-486D-B1C9-A0DA74E03356}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
@@ -820,53 +1109,61 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="C10" t="s">
         <v>11</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D10" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="D10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="D11" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="D12" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H12" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="D13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="D14" t="s">
         <v>15</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F14" t="s">
         <v>30</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H14" t="s">
         <v>31</v>
       </c>
     </row>
@@ -878,7 +1175,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F096B9D8-F958-4268-B6BD-A20FCF680D12}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
@@ -888,7 +1185,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
@@ -903,82 +1200,233 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11">
-        <v>2</v>
-      </c>
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A12">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13">
-        <v>4</v>
-      </c>
-      <c r="B13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B14" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B20" s="1" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B27" s="1" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B29" s="1"/>
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B30" s="1"/>
+      <c r="D30">
+        <v>3</v>
+      </c>
+      <c r="E30" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E33">
+        <v>2</v>
+      </c>
+      <c r="F33" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E34">
+        <v>3</v>
+      </c>
+      <c r="F34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F35" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="F38" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E39">
+        <v>3</v>
+      </c>
+      <c r="F39" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E40">
+        <v>4</v>
+      </c>
+      <c r="F40" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/仕様書ほか.xlsx
+++ b/仕様書ほか.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\katoy\i2c_use_memory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB4C83B-39C5-4CF6-9C4C-5FA6C3F8A528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4AACD1-CFD5-4AE8-9341-59A3F6B94265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43455" yWindow="0" windowWidth="14250" windowHeight="8205" activeTab="1" xr2:uid="{F144D80B-630C-43F9-9D23-4AE66E7F3353}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="12810" activeTab="1" xr2:uid="{F144D80B-630C-43F9-9D23-4AE66E7F3353}"/>
   </bookViews>
   <sheets>
     <sheet name="仕様書" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="81">
   <si>
     <t>1, 概要</t>
     <rPh sb="3" eb="5">
@@ -660,6 +660,169 @@
     </rPh>
     <rPh sb="17" eb="18">
       <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（for文の1..255でも可、ただ255の部分に変数を挿入はできない）</t>
+  </si>
+  <si>
+    <t>オリジナルi2cget関数</t>
+    <rPh sb="11" eb="13">
+      <t>カンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その引数のアドレスでi2cgetをする</t>
+    <rPh sb="2" eb="4">
+      <t>ヒキスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出力から0xを取り除く</t>
+    <rPh sb="0" eb="2">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小文字を大文字に変換する</t>
+    <rPh sb="0" eb="3">
+      <t>コモジ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>オオモジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヘンカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:、01:（引数）を付け足す</t>
+    <rPh sb="8" eb="10">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF6A9955"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>#trを自分で作ろうとした残がい</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF6A9955"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>#for i in 0 1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF6A9955"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>#do</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF6A9955"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>#for alfa in {a..z}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF6A9955"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>#if [ ${$cut_result:$i:1} = $alfa ]; then</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF6A9955"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>#big_${!((1 - $i))}jou=</t>
+    </r>
+  </si>
+  <si>
+    <t>➡</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ここで、変数名に変数を挿入する方法が知りたかった。</t>
+    <rPh sb="4" eb="7">
+      <t>ヘンスウメイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ソウニュウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>シ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -668,7 +831,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -683,6 +846,18 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF6A9955"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -707,11 +882,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1175,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F096B9D8-F958-4268-B6BD-A20FCF680D12}">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
@@ -1235,198 +1416,277 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B15" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B17" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A18">
         <v>1</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A19">
         <v>2</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A20">
         <v>3</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B20" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A21">
         <v>4</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B21" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B22" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B22" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B23" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
         <v>32</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B27" s="1" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B28" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B29" s="1"/>
       <c r="D29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B30" s="1"/>
       <c r="D30">
+        <v>2</v>
+      </c>
+      <c r="E30" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B31" s="1"/>
+      <c r="D31">
         <v>3</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E31" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" t="s">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
         <v>60</v>
       </c>
-      <c r="E32">
+      <c r="E33">
         <v>1</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F33" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="E33">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="E34">
         <v>2</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F34" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="E34">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="E35">
         <v>3</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F35" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="F35" t="s">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="F36" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" t="s">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
         <v>61</v>
       </c>
-      <c r="E37">
+      <c r="E38">
         <v>1</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F38" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="E38">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="E39">
         <v>2</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F39" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="E39">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="E40">
         <v>3</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F40" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="E40">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="E41">
         <v>4</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F41" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A42" t="s">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
+        <v>51</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="D44">
+        <v>2</v>
+      </c>
+      <c r="E44" t="s">
+        <v>69</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="D45">
+        <v>3</v>
+      </c>
+      <c r="E45" t="s">
+        <v>70</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="D46">
+        <v>4</v>
+      </c>
+      <c r="E46" t="s">
+        <v>71</v>
+      </c>
+      <c r="H46" t="s">
+        <v>79</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="D47">
+        <v>5</v>
+      </c>
+      <c r="E47" t="s">
+        <v>72</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="I48" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="N48" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
         <v>47</v>
       </c>
-      <c r="C42">
+      <c r="C50">
         <v>1</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D50" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="C43">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C51">
         <v>2</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D51" t="s">
         <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="D52" s="2" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/仕様書ほか.xlsx
+++ b/仕様書ほか.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\katoy\i2c_use_memory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4AACD1-CFD5-4AE8-9341-59A3F6B94265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7201B5-BC5D-429F-A762-171D5ECB80DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="12810" activeTab="1" xr2:uid="{F144D80B-630C-43F9-9D23-4AE66E7F3353}"/>
+    <workbookView xWindow="1875" yWindow="1125" windowWidth="14325" windowHeight="14280" xr2:uid="{F144D80B-630C-43F9-9D23-4AE66E7F3353}"/>
   </bookViews>
   <sheets>
     <sheet name="仕様書" sheetId="1" r:id="rId1"/>
     <sheet name="設計書" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="120">
   <si>
     <t>1, 概要</t>
     <rPh sb="3" eb="5">
@@ -375,19 +376,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>全てのデータをアドレス順に表示する。</t>
-    <rPh sb="0" eb="1">
-      <t>スベ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ジュン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>アドレス最大値定義（for文用、16進数）</t>
     <rPh sb="4" eb="7">
       <t>サイダイチ</t>
@@ -703,19 +691,6 @@
     </rPh>
     <rPh sb="8" eb="10">
       <t>ヘンカン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>00:、01:（引数）を付け足す</t>
-    <rPh sb="8" eb="10">
-      <t>ヒキスウ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>タ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -824,6 +799,242 @@
     <rPh sb="18" eb="19">
       <t>シ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全てのデータをアドレス順に、csv形式で表示する。</t>
+    <rPh sb="0" eb="1">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>16刻みcsv出力関数</t>
+    <rPh sb="2" eb="3">
+      <t>キザ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>16刻みリスト出力関数</t>
+    <rPh sb="2" eb="3">
+      <t>キザ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>シュツリョクカンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出力する。</t>
+    <rPh sb="0" eb="2">
+      <t>シュツリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第2引数あり：00:（アドレス）を付け足す</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ローカルで引数を定義する（アドレス）</t>
+    <rPh sb="5" eb="7">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リストが無ければ新しくリストを作り、00を入れる。</t>
+    <rPh sb="4" eb="5">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リストにすでに17個データがあれば、リストを表示してからリストを削除し、</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>先頭の値に1を足して作り直す。</t>
+  </si>
+  <si>
+    <t>リストに、オリジナルi2cgetのデータを加える</t>
+    <rPh sb="21" eb="22">
+      <t>クワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第2引数がある場合、残っているリストを表示してリストを消す</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リストtoＣＳＶ関数</t>
+    <rPh sb="8" eb="10">
+      <t>カンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>listの空白をコンマに変換する</t>
+    <rPh sb="5" eb="7">
+      <t>クウハク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヘンカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上の文字列を出力する。</t>
+    <rPh sb="0" eb="1">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シュツリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ローカルで引数を定義する（リスト）</t>
+    <rPh sb="5" eb="7">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>real    0m 7.54s</t>
+  </si>
+  <si>
+    <t>user    0m 3.44s</t>
+  </si>
+  <si>
+    <t>sys     0m 3.51s</t>
+  </si>
+  <si>
+    <t>bef1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>real    0m 9.67s</t>
+  </si>
+  <si>
+    <t>user    0m 4.44s</t>
+  </si>
+  <si>
+    <t>sys     0m 4.48s</t>
+  </si>
+  <si>
+    <t>bef2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>real    0m 10.92s</t>
+  </si>
+  <si>
+    <t>user    0m 4.96s</t>
+  </si>
+  <si>
+    <t>sys     0m 5.16s</t>
+  </si>
+  <si>
+    <t>bef3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>real    0m 10.86s</t>
+  </si>
+  <si>
+    <t>sys     0m 5.17s</t>
+  </si>
+  <si>
+    <t>real    0m 9.66s</t>
+  </si>
+  <si>
+    <t>user    0m 4.80s</t>
+  </si>
+  <si>
+    <t>sys     0m 4.21s</t>
+  </si>
+  <si>
+    <t>i2cstop</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>unsetstop</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>real    0m 3.89s</t>
+  </si>
+  <si>
+    <t>user    0m 1.76s</t>
+  </si>
+  <si>
+    <t>sys     0m 1.82s</t>
+  </si>
+  <si>
+    <t>real    0m 9.42s</t>
+  </si>
+  <si>
+    <t>user    0m 4.73s</t>
+  </si>
+  <si>
+    <t>sys     0m 4.11s</t>
+  </si>
+  <si>
+    <t>CSVstop</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1293,7 +1504,7 @@
         <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
@@ -1356,337 +1567,546 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F096B9D8-F958-4268-B6BD-A20FCF680D12}">
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:N65"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B16" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B18" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A18">
-        <v>1</v>
-      </c>
-      <c r="B18" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A22">
         <v>4</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B22" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B24" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
         <v>32</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B28" s="1" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B29" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" s="1"/>
-      <c r="D29">
-        <v>1</v>
-      </c>
-      <c r="E29" t="s">
-        <v>52</v>
-      </c>
-    </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>58</v>
+      </c>
       <c r="B30" s="1"/>
       <c r="D30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B31" s="1"/>
       <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B32" s="1"/>
+      <c r="D32">
         <v>3</v>
       </c>
-      <c r="E31" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A33" t="s">
+      <c r="E32" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>59</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="F35" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="E36">
+        <v>3</v>
+      </c>
+      <c r="F36" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="F37" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
         <v>60</v>
       </c>
-      <c r="E33">
+      <c r="E39">
         <v>1</v>
       </c>
-      <c r="F33" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="E34">
+      <c r="F39" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="E40">
         <v>2</v>
       </c>
-      <c r="F34" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="E35">
+      <c r="F40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="E41">
         <v>3</v>
       </c>
-      <c r="F35" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="F36" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A38" t="s">
-        <v>61</v>
-      </c>
-      <c r="E38">
+      <c r="F41" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="E42">
+        <v>4</v>
+      </c>
+      <c r="F42" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>67</v>
+      </c>
+      <c r="D44">
         <v>1</v>
       </c>
-      <c r="F38" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="E39">
+      <c r="E44" t="s">
+        <v>50</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="D45">
         <v>2</v>
       </c>
-      <c r="F39" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="E40">
+      <c r="E45" t="s">
+        <v>68</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="D46">
         <v>3</v>
       </c>
-      <c r="F40" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="E41">
+      <c r="E46" t="s">
+        <v>69</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="D47">
         <v>4</v>
       </c>
-      <c r="F41" t="s">
+      <c r="E47" t="s">
+        <v>70</v>
+      </c>
+      <c r="H47" t="s">
+        <v>77</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="D48">
+        <v>5</v>
+      </c>
+      <c r="E48" t="s">
+        <v>82</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="E49" t="s">
+        <v>83</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="N49" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>90</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="C52">
+        <v>2</v>
+      </c>
+      <c r="D52" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="C53">
+        <v>3</v>
+      </c>
+      <c r="D53" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A55" t="s">
+        <v>81</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="C56">
+        <v>2</v>
+      </c>
+      <c r="D56" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="D58" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="D59" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="C60">
+        <v>4</v>
+      </c>
+      <c r="D60" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A63" t="s">
+        <v>46</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A43" t="s">
-        <v>68</v>
-      </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
-      <c r="E43" t="s">
-        <v>51</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="D44">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="C64">
         <v>2</v>
       </c>
-      <c r="E44" t="s">
-        <v>69</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="D45">
-        <v>3</v>
-      </c>
-      <c r="E45" t="s">
-        <v>70</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="D46">
-        <v>4</v>
-      </c>
-      <c r="E46" t="s">
-        <v>71</v>
-      </c>
-      <c r="H46" t="s">
-        <v>79</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="D47">
-        <v>5</v>
-      </c>
-      <c r="E47" t="s">
-        <v>72</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="I48" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="N48" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A50" t="s">
-        <v>47</v>
-      </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="D64" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C51">
-        <v>2</v>
-      </c>
-      <c r="D51" t="s">
+    <row r="65" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D65" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="D52" s="2" t="s">
-        <v>67</v>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D53D7DDE-98E2-44D6-B0DE-565BF1C36A59}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="2" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="D11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="D12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="D13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="D14" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/仕様書ほか.xlsx
+++ b/仕様書ほか.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\katoy\i2c_use_memory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7201B5-BC5D-429F-A762-171D5ECB80DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F6AADDB-1ECB-4E81-B93F-BD758268B28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1875" yWindow="1125" windowWidth="14325" windowHeight="14280" xr2:uid="{F144D80B-630C-43F9-9D23-4AE66E7F3353}"/>
+    <workbookView xWindow="14700" yWindow="1185" windowWidth="20655" windowHeight="14280" activeTab="1" xr2:uid="{F144D80B-630C-43F9-9D23-4AE66E7F3353}"/>
   </bookViews>
   <sheets>
     <sheet name="仕様書" sheetId="1" r:id="rId1"/>
@@ -639,19 +639,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>カウントアップさせた値を16進数に戻してi2cgetをする</t>
-    <rPh sb="10" eb="11">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>シンスウ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>モド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>（for文の1..255でも可、ただ255の部分に変数を挿入はできない）</t>
   </si>
   <si>
@@ -852,68 +839,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ローカルで引数を定義する（アドレス）</t>
-    <rPh sb="5" eb="7">
-      <t>ヒキスウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>テイギ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>リストが無ければ新しくリストを作り、00を入れる。</t>
-    <rPh sb="4" eb="5">
-      <t>ナ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>アタラ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>イ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>リストにすでに17個データがあれば、リストを表示してからリストを削除し、</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>先頭の値に1を足して作り直す。</t>
-  </si>
-  <si>
-    <t>リストに、オリジナルi2cgetのデータを加える</t>
-    <rPh sb="21" eb="22">
-      <t>クワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>第2引数がある場合、残っているリストを表示してリストを消す</t>
-    <rPh sb="0" eb="1">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ヒキスウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ノコ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>ケ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>リストtoＣＳＶ関数</t>
     <rPh sb="8" eb="10">
       <t>カンスウ</t>
@@ -1035,6 +960,139 @@
   </si>
   <si>
     <t>CSVstop</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ローカルで引数を定義する（カウントアップ10進数、最終アドレス）</t>
+    <rPh sb="5" eb="7">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シンスウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>サイシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>i2cgetのデータを文字列右横に追加する</t>
+    <rPh sb="11" eb="14">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ミギヨコ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カウントアップを16で割り、リセット基準とのずれを定義する</t>
+    <rPh sb="11" eb="12">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>キジュン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オフセットが15の場合、たまった文字列を吐き出す</t>
+    <rPh sb="9" eb="11">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オフセットが0の場合、先頭に現在のアドレスを入れた新しい文字列を始める</t>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セントウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="28" eb="31">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今のアドレスが最終アドレスだった場合、たまった文字列を吐き出す</t>
+    <rPh sb="0" eb="1">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サイシュウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カウントアップさせた値を16進数に戻して、最終アドレスとともに16刻みリスト出力関数に渡す</t>
+    <rPh sb="10" eb="11">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シンスウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>サイシュウ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>キザ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ワタ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1504,7 +1562,7 @@
         <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
@@ -1627,12 +1685,12 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
@@ -1814,7 +1872,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -1823,7 +1881,7 @@
         <v>50</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.4">
@@ -1831,10 +1889,10 @@
         <v>2</v>
       </c>
       <c r="E45" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.4">
@@ -1842,10 +1900,10 @@
         <v>3</v>
       </c>
       <c r="E46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.4">
@@ -1853,13 +1911,13 @@
         <v>4</v>
       </c>
       <c r="E47" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H47" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.4">
@@ -1867,32 +1925,32 @@
         <v>5</v>
       </c>
       <c r="E48" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.4">
       <c r="E49" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.4">
@@ -1900,7 +1958,7 @@
         <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.4">
@@ -1908,18 +1966,18 @@
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C55">
         <v>1</v>
       </c>
       <c r="D55" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.4">
@@ -1927,7 +1985,7 @@
         <v>2</v>
       </c>
       <c r="D56" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.4">
@@ -1935,25 +1993,28 @@
         <v>3</v>
       </c>
       <c r="D57" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="C58">
+        <v>4</v>
+      </c>
       <c r="D58" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="C59">
+        <v>5</v>
+      </c>
       <c r="D59" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="C60">
-        <v>4</v>
-      </c>
       <c r="D60" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.4">
@@ -1972,12 +2033,12 @@
         <v>2</v>
       </c>
       <c r="D64" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65" spans="4:4" x14ac:dyDescent="0.4">
       <c r="D65" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1998,58 +2059,58 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" t="s">
         <v>105</v>
-      </c>
-      <c r="D1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" t="s">
         <v>100</v>
-      </c>
-      <c r="C4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D4" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -2059,54 +2120,54 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="D11" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="D12" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="D13" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="D14" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/仕様書ほか.xlsx
+++ b/仕様書ほか.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\katoy\i2c_use_memory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F6AADDB-1ECB-4E81-B93F-BD758268B28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E939F1F-B3EB-43B0-B54D-CC8B3DF7A6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14700" yWindow="1185" windowWidth="20655" windowHeight="14280" activeTab="1" xr2:uid="{F144D80B-630C-43F9-9D23-4AE66E7F3353}"/>
+    <workbookView xWindow="31215" yWindow="780" windowWidth="26310" windowHeight="14280" activeTab="1" xr2:uid="{F144D80B-630C-43F9-9D23-4AE66E7F3353}"/>
   </bookViews>
   <sheets>
     <sheet name="仕様書" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="151">
   <si>
     <t>1, 概要</t>
     <rPh sb="3" eb="5">
@@ -1095,12 +1095,352 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>-r</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-w</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>csvファイル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>指定された行の値をすべて書き換える</t>
+    <rPh sb="0" eb="2">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ギョウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>拡張子違い</t>
+    <rPh sb="0" eb="3">
+      <t>カクチョウシ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>チガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（ファイルの内部で列数まちがい、桁数まちがい、文字間違いがありうる。</t>
+    <rPh sb="6" eb="8">
+      <t>ナイブ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>レツスウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ケタスウ</t>
+    </rPh>
+    <rPh sb="23" eb="27">
+      <t>モジマチガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このチェックをどうするか、どうreadと一緒にするかは次の課題。）</t>
+    <rPh sb="20" eb="22">
+      <t>イッショ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>カダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↑そもそもこのモードの引数もエラーチェックしなきゃいけんのだな。</t>
+    <rPh sb="11" eb="13">
+      <t>ヒキスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>見本の文字列も変更が必要だし、エラーメッセージがより複雑になる。</t>
+    <rPh sb="0" eb="2">
+      <t>ミホン</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>フクザツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この場合、version１からどんなふうに変更を見せればいいのか難しいところだな。</t>
+    <rPh sb="2" eb="4">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ムズカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘルプの中の文字も変数で代入する形か。</t>
+    <rPh sb="4" eb="5">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ダイニュウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カタチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>par2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>もしくは、思い切って分けちゃったほうがいい。</t>
+    <rPh sb="5" eb="6">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エラーメッセージ5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パラメータなし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エラーメッセージ6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>存在しないファイル</t>
+    <rPh sb="0" eb="2">
+      <t>ソンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エラーメッセージ7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>➡メインループのelseでエラーを書く。（エラーメッセージ8）</t>
+    <rPh sb="17" eb="18">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>➡今回はwriteonlyということで</t>
+    <rPh sb="1" eb="3">
+      <t>コンカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>引数は一つでやります。-wのほうだけ実装！！</t>
+    <rPh sb="0" eb="2">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>使用可能なファイルを正規表現で定義（.csv）</t>
+    <rPh sb="0" eb="4">
+      <t>シヨウカノウ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>セイキヒョウゲン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>csv書き込み関数</t>
+    <rPh sb="3" eb="4">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>i2cライン番号定義</t>
+    <rPh sb="6" eb="8">
+      <t>バンゴウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メモリーアドレス定義</t>
+    <rPh sb="8" eb="10">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CSV書き込み関数</t>
+    <rPh sb="3" eb="4">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CSVファイルを読み込み、アドレスとデータを分離する</t>
+    <rPh sb="8" eb="9">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ブンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>i2csetにfor文か何かで回して1行分データを入れる。</t>
+    <rPh sb="10" eb="11">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ギョウブン</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>結果をechoで1行として吐き出す（入力したものと全く同じになるわけだが）。</t>
+    <rPh sb="0" eb="2">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ギョウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>マッタ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>オナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>末尾に空白行がなければ追加する</t>
+    <rPh sb="0" eb="2">
+      <t>マツビ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>クウハクギョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>csvファイル読み込み先定義</t>
+    <rPh sb="7" eb="8">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1128,13 +1468,35 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1151,7 +1513,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1162,6 +1524,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1179,6 +1550,71 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>171449</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>161924</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>295274</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="乗算記号 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBC7B6D8-1EF4-22A9-1F9C-E41E5352EE82}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1142999" y="5162549"/>
+          <a:ext cx="4238625" cy="2600325"/>
+        </a:xfrm>
+        <a:prstGeom prst="mathMultiply">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1498,7 +1934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBAE3C68-FE4B-486D-B1C9-A0DA74E03356}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
@@ -1540,7 +1976,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
@@ -1550,13 +1986,16 @@
       <c r="B8" t="s">
         <v>9</v>
       </c>
+      <c r="C8" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="B9" t="s">
-        <v>9</v>
+      <c r="B9" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
@@ -1617,15 +2056,109 @@
         <v>31</v>
       </c>
     </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B16" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="D17" t="s">
+        <v>134</v>
+      </c>
+      <c r="F17" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="D19" t="s">
+        <v>124</v>
+      </c>
+      <c r="F19" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="D20" t="s">
+        <v>136</v>
+      </c>
+      <c r="F20" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="D21" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="D22" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B24" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B25" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B28" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B29" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B30" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B31" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D33" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D34" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F096B9D8-F958-4268-B6BD-A20FCF680D12}">
-  <dimension ref="A1:N65"/>
+  <dimension ref="A1:N79"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -1659,385 +2192,445 @@
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>43</v>
+      <c r="A7" s="6" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>55</v>
+      <c r="A10" s="6" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A19" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B17" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B23" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B18" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B24" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A19">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A25">
         <v>1</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B25" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A20">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A26">
         <v>2</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B26" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A21">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A27">
         <v>3</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A22">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A28">
         <v>4</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B28" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B23" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B29" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B24" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B30" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
         <v>32</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B34" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B29" s="1" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B35" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="D30">
+      <c r="B36" s="1"/>
+      <c r="D36">
         <v>1</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E36" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B31" s="1"/>
-      <c r="D31">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B37" s="1"/>
+      <c r="D37">
         <v>2</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E37" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B32" s="1"/>
-      <c r="D32">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B38" s="1"/>
+      <c r="D38">
         <v>3</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E38" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A34" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
         <v>59</v>
       </c>
-      <c r="E34">
+      <c r="E40">
         <v>1</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F40" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="E35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E41">
         <v>2</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F41" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="E36">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E42">
         <v>3</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F42" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="F37" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F43" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A39" t="s">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
         <v>60</v>
       </c>
-      <c r="E39">
+      <c r="E45">
         <v>1</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F45" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="E40">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E46">
         <v>2</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F46" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="E41">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E47">
         <v>3</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F47" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="E42">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E48">
         <v>4</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F48" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A44" t="s">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
         <v>66</v>
       </c>
-      <c r="D44">
+      <c r="D50">
         <v>1</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E50" t="s">
         <v>50</v>
       </c>
-      <c r="I44" s="3" t="s">
+      <c r="I50" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="D45">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="D51">
         <v>2</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E51" t="s">
         <v>67</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="I51" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="D46">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="D52">
         <v>3</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E52" t="s">
         <v>68</v>
       </c>
-      <c r="I46" s="3" t="s">
+      <c r="I52" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="D47">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="D53">
         <v>4</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E53" t="s">
         <v>69</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H53" t="s">
         <v>76</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="I53" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="D48">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="D54">
         <v>5</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E54" t="s">
         <v>81</v>
       </c>
-      <c r="I48" s="3" t="s">
+      <c r="I54" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="E49" t="s">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="E55" t="s">
         <v>82</v>
       </c>
-      <c r="I49" s="3" t="s">
+      <c r="I55" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="N49" t="s">
+      <c r="N55" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A51" t="s">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
         <v>83</v>
       </c>
-      <c r="C51">
+      <c r="C57">
         <v>1</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D57" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="C52">
-        <v>2</v>
-      </c>
-      <c r="D52" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="C53">
-        <v>3</v>
-      </c>
-      <c r="D53" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A55" t="s">
-        <v>80</v>
-      </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-      <c r="D55" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="C56">
-        <v>2</v>
-      </c>
-      <c r="D56" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="C57">
-        <v>3</v>
-      </c>
-      <c r="D57" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.4">
       <c r="C58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D58" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.4">
       <c r="C59">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D59" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="D60" t="s">
-        <v>118</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>80</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A63" t="s">
-        <v>46</v>
-      </c>
       <c r="C63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D63" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.4">
       <c r="C64">
+        <v>4</v>
+      </c>
+      <c r="D64" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C65">
+        <v>5</v>
+      </c>
+      <c r="D65" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="D66" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A68" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+      <c r="D68" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C69">
         <v>2</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D69" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C70">
+        <v>3</v>
+      </c>
+      <c r="D70" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C71">
+        <v>4</v>
+      </c>
+      <c r="D71" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A77" t="s">
+        <v>46</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C78">
+        <v>2</v>
+      </c>
+      <c r="D78" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="65" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D65" s="2" t="s">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="D79" s="2" t="s">
         <v>65</v>
       </c>
     </row>

--- a/仕様書ほか.xlsx
+++ b/仕様書ほか.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\katoy\i2c_use_memory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E939F1F-B3EB-43B0-B54D-CC8B3DF7A6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB12727A-B3CE-469F-A87B-4F6294AC132B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31215" yWindow="780" windowWidth="26310" windowHeight="14280" activeTab="1" xr2:uid="{F144D80B-630C-43F9-9D23-4AE66E7F3353}"/>
+    <workbookView xWindow="42405" yWindow="0" windowWidth="15300" windowHeight="16305" activeTab="1" xr2:uid="{F144D80B-630C-43F9-9D23-4AE66E7F3353}"/>
   </bookViews>
   <sheets>
     <sheet name="仕様書" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="153">
   <si>
     <t>1, 概要</t>
     <rPh sb="3" eb="5">
@@ -301,19 +301,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>i2cgetに入力された引数を渡す。</t>
-    <rPh sb="7" eb="9">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ヒキスウ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ワタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>引数に応じたエラーメッセージの表示。</t>
     <rPh sb="0" eb="2">
       <t>ヒキスウ</t>
@@ -395,22 +382,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>引数が無い場合全表示する。</t>
-    <rPh sb="0" eb="2">
-      <t>ヒキスウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ナ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="7" eb="10">
-      <t>ゼンヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>引数が規定より多いこと。</t>
     <rPh sb="0" eb="2">
       <t>ヒキスウ</t>
@@ -421,32 +392,6 @@
     <t>データ全表示関数</t>
   </si>
   <si>
-    <t>parを桁ごとに分解する</t>
-    <rPh sb="4" eb="5">
-      <t>ケタ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ブンカイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>上記の結果をすべて足す</t>
-    <rPh sb="0" eb="2">
-      <t>ジョウキ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ケッカ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>タ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>16進数一桁分変換関数</t>
-  </si>
-  <si>
     <t>ローカルで引数を定義する</t>
     <rPh sb="5" eb="7">
       <t>ヒキスウ</t>
@@ -457,75 +402,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ローカルで引数を定義する。</t>
-    <rPh sb="5" eb="7">
-      <t>ヒキスウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>テイギ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>桁ごとに16の乗数を掛け算する</t>
-    <rPh sb="0" eb="1">
-      <t>ケタ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ジョウスウ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ザン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>for文で、parが0～15のとき、0～Fをechoするようにする。</t>
-    <rPh sb="3" eb="4">
-      <t>ブン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>for文で、parがA～Fのとき、10～15をechoするようにする。</t>
-    <rPh sb="3" eb="4">
-      <t>ブン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2桁の16進数を10進数に変える関数定義（while文用）</t>
-    <rPh sb="16" eb="18">
-      <t>カンスウ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>テイギ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ブンヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>255までの10進数を16進数に変える関数定義（while文用）</t>
-    <rPh sb="19" eb="21">
-      <t>カンスウ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>テイギ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>ヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>データ全表示関数（while文）</t>
     <rPh sb="3" eb="6">
       <t>ゼンヒョウジ</t>
@@ -535,84 +411,6 @@
     </rPh>
     <rPh sb="14" eb="15">
       <t>ブン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>16進数一桁分変換関数</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2桁の16進数を10進数に変換する関数</t>
-    <rPh sb="1" eb="2">
-      <t>ケタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>255までの10進数を16進数に変換する関数</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>16で剰余を出し、0乗目の値として変数に定義する。</t>
-    <rPh sb="3" eb="5">
-      <t>ジョウヨ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ジョウ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ヘンスウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>テイギ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>16で商を出し、1乗目の値として変数に定義する。</t>
-    <rPh sb="3" eb="4">
-      <t>ショウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ジョウメ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ヘンスウ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>テイギ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>商・あまりの順で並べて表示する。</t>
-    <rPh sb="0" eb="1">
-      <t>ショウ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ジュン</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ナラ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1432,6 +1230,145 @@
     </rPh>
     <rPh sb="12" eb="14">
       <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>r</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>w</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>read_oneadr</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>read_alladr</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>write_fromcsv</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>read_lineadr</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第一引数が-w</t>
+    <rPh sb="0" eb="2">
+      <t>ダイイチ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒキスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第一引数が-r</t>
+    <rPh sb="0" eb="2">
+      <t>ダイイチ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒキスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第2引数がなければ全表示</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ゼンヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>引数がないこと。</t>
+    <rPh sb="0" eb="2">
+      <t>ヒキスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>csvファイルではないこと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>指定したファイルが存在しないこと</t>
+    <rPh sb="0" eb="2">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ソンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>read_oneadrに入力された引数を渡す。</t>
+    <rPh sb="12" eb="14">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ワタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>write_fromcsvに入力された引数を渡す。</t>
+    <rPh sb="14" eb="16">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ワタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>←</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>read時のパラメータエラー</t>
+    <rPh sb="4" eb="5">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>write時のパラメータエラー</t>
+    <rPh sb="5" eb="6">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>引数の個数が多いエラー</t>
+    <rPh sb="0" eb="2">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コスウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オオ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1485,18 +1422,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1532,7 +1463,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1987,7 +1918,7 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
@@ -1995,13 +1926,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
@@ -2058,21 +1989,21 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B16" s="1" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.4">
       <c r="D17" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="F17" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.4">
@@ -2085,68 +2016,68 @@
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.4">
       <c r="D19" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="F19" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.4">
       <c r="D20" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="F20" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.4">
       <c r="D21" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.4">
       <c r="D22" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B24" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B25" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B28" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B29" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B30" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B31" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.4">
       <c r="D33" s="4" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="4:4" x14ac:dyDescent="0.4">
       <c r="D34" s="5" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -2158,480 +2089,456 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F096B9D8-F958-4268-B6BD-A20FCF680D12}">
-  <dimension ref="A1:N79"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B13" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="E16" t="s">
+        <v>134</v>
+      </c>
+      <c r="F16" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+        <v>62</v>
+      </c>
+      <c r="E17" t="s">
+        <v>134</v>
+      </c>
+      <c r="F17" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+        <v>46</v>
+      </c>
+      <c r="E18" t="s">
+        <v>134</v>
+      </c>
+      <c r="F18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A19" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+        <v>125</v>
+      </c>
+      <c r="E19" t="s">
+        <v>135</v>
+      </c>
+      <c r="F19" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B23" t="s">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="C23" t="s">
+        <v>148</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+      <c r="H23" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B24" t="s">
+        <v>141</v>
+      </c>
+      <c r="I24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B26" t="s">
+        <v>142</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B27" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27">
+        <v>2</v>
+      </c>
+      <c r="I27" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <v>1</v>
+      </c>
+      <c r="B28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H28">
+        <v>3</v>
+      </c>
+      <c r="I28" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <v>3</v>
+      </c>
+      <c r="B30" t="s">
+        <v>36</v>
+      </c>
+      <c r="I30" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B32" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="B38" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="B39" s="1"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>49</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41" t="s">
+        <v>45</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="D42">
+        <v>2</v>
+      </c>
+      <c r="E42" t="s">
+        <v>50</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="D43">
+        <v>3</v>
+      </c>
+      <c r="E43" t="s">
+        <v>51</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="D44">
+        <v>4</v>
+      </c>
+      <c r="E44" t="s">
+        <v>52</v>
+      </c>
+      <c r="H44" t="s">
+        <v>59</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="D45">
+        <v>5</v>
+      </c>
+      <c r="E45" t="s">
+        <v>64</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="E46" t="s">
+        <v>65</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N46" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C49">
+        <v>2</v>
+      </c>
+      <c r="D49" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C50">
+        <v>3</v>
+      </c>
+      <c r="D50" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>63</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C54">
+        <v>3</v>
+      </c>
+      <c r="D54" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C55">
+        <v>4</v>
+      </c>
+      <c r="D55" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C56">
+        <v>5</v>
+      </c>
+      <c r="D56" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="D57" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B24" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A25">
+      <c r="C59">
         <v>1</v>
       </c>
-      <c r="B25" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A26">
+      <c r="D59" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C60">
         <v>2</v>
       </c>
-      <c r="B26" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A27">
+      <c r="D60" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="D61" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A64" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+      <c r="D64" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="65" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C65">
+        <v>2</v>
+      </c>
+      <c r="D65" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="66" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C66">
         <v>3</v>
       </c>
-      <c r="B27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A28">
+      <c r="D66" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="67" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C67">
         <v>4</v>
       </c>
-      <c r="B28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B29" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B30" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A33" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A34" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B35" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" t="s">
-        <v>58</v>
-      </c>
-      <c r="B36" s="1"/>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="E36" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B37" s="1"/>
-      <c r="D37">
-        <v>2</v>
-      </c>
-      <c r="E37" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B38" s="1"/>
-      <c r="D38">
-        <v>3</v>
-      </c>
-      <c r="E38" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A40" t="s">
-        <v>59</v>
-      </c>
-      <c r="E40">
-        <v>1</v>
-      </c>
-      <c r="F40" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="E41">
-        <v>2</v>
-      </c>
-      <c r="F41" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="E42">
-        <v>3</v>
-      </c>
-      <c r="F42" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="F43" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A45" t="s">
-        <v>60</v>
-      </c>
-      <c r="E45">
-        <v>1</v>
-      </c>
-      <c r="F45" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="E46">
-        <v>2</v>
-      </c>
-      <c r="F46" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="E47">
-        <v>3</v>
-      </c>
-      <c r="F47" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="E48">
-        <v>4</v>
-      </c>
-      <c r="F48" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A50" t="s">
-        <v>66</v>
-      </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-      <c r="E50" t="s">
-        <v>50</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="D51">
-        <v>2</v>
-      </c>
-      <c r="E51" t="s">
-        <v>67</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="D52">
-        <v>3</v>
-      </c>
-      <c r="E52" t="s">
-        <v>68</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="D53">
-        <v>4</v>
-      </c>
-      <c r="E53" t="s">
-        <v>69</v>
-      </c>
-      <c r="H53" t="s">
-        <v>76</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="D54">
-        <v>5</v>
-      </c>
-      <c r="E54" t="s">
-        <v>81</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="E55" t="s">
-        <v>82</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="N55" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A57" t="s">
-        <v>83</v>
-      </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
-      <c r="D57" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="C58">
-        <v>2</v>
-      </c>
-      <c r="D58" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="C59">
-        <v>3</v>
-      </c>
-      <c r="D59" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A61" t="s">
-        <v>80</v>
-      </c>
-      <c r="C61">
-        <v>1</v>
-      </c>
-      <c r="D61" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="C62">
-        <v>2</v>
-      </c>
-      <c r="D62" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="C63">
-        <v>3</v>
-      </c>
-      <c r="D63" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="C64">
-        <v>4</v>
-      </c>
-      <c r="D64" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C65">
-        <v>5</v>
-      </c>
-      <c r="D65" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="D66" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A68" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C68">
-        <v>1</v>
-      </c>
-      <c r="D68" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C69">
-        <v>2</v>
-      </c>
-      <c r="D69" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C70">
-        <v>3</v>
-      </c>
-      <c r="D70" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C71">
-        <v>4</v>
-      </c>
-      <c r="D71" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A77" t="s">
-        <v>46</v>
-      </c>
-      <c r="C77">
-        <v>1</v>
-      </c>
-      <c r="D77" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C78">
-        <v>2</v>
-      </c>
-      <c r="D78" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="D79" s="2" t="s">
-        <v>65</v>
+      <c r="D67" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2652,58 +2559,58 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="B1" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C1" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D1" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -2713,54 +2620,54 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="D11" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="D12" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="D13" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="D14" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/仕様書ほか.xlsx
+++ b/仕様書ほか.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\katoy\i2c_use_memory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB12727A-B3CE-469F-A87B-4F6294AC132B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD93590-2827-46DF-A189-8C667F4836F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42405" yWindow="0" windowWidth="15300" windowHeight="16305" activeTab="1" xr2:uid="{F144D80B-630C-43F9-9D23-4AE66E7F3353}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="16305" activeTab="1" xr2:uid="{F144D80B-630C-43F9-9D23-4AE66E7F3353}"/>
   </bookViews>
   <sheets>
     <sheet name="仕様書" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="150">
   <si>
     <t>1, 概要</t>
     <rPh sb="3" eb="5">
@@ -137,16 +137,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>パラメータ2個以上</t>
-    <rPh sb="6" eb="7">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>イジョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>2文字以上</t>
     <rPh sb="1" eb="3">
       <t>モジ</t>
@@ -226,31 +216,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>エラーメッセージ2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>（16進数であるため、記号やG－Z は使えないこと）</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>エラーメッセージ1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>（パラメータが規定より多いこと）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エラーメッセージ3</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>（2桁まで）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エラーメッセージ4</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -378,13 +348,6 @@
     </rPh>
     <rPh sb="18" eb="20">
       <t>シンスウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>引数が規定より多いこと。</t>
-    <rPh sb="0" eb="2">
-      <t>ヒキスウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -964,93 +927,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>↑そもそもこのモードの引数もエラーチェックしなきゃいけんのだな。</t>
-    <rPh sb="11" eb="13">
-      <t>ヒキスウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>見本の文字列も変更が必要だし、エラーメッセージがより複雑になる。</t>
-    <rPh sb="0" eb="2">
-      <t>ミホン</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>モジレツ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヒツヨウ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>フクザツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>この場合、version１からどんなふうに変更を見せればいいのか難しいところだな。</t>
-    <rPh sb="2" eb="4">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>ムズカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヘルプの中の文字も変数で代入する形か。</t>
-    <rPh sb="4" eb="5">
-      <t>ナカ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ヘンスウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ダイニュウ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>カタチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>par2</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>もしくは、思い切って分けちゃったほうがいい。</t>
-    <rPh sb="5" eb="6">
-      <t>オモ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エラーメッセージ5</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>パラメータなし</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エラーメッセージ6</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1061,37 +942,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>エラーメッセージ7</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>➡メインループのelseでエラーを書く。（エラーメッセージ8）</t>
-    <rPh sb="17" eb="18">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>➡今回はwriteonlyということで</t>
-    <rPh sb="1" eb="3">
-      <t>コンカイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>引数は一つでやります。-wのほうだけ実装！！</t>
-    <rPh sb="0" eb="2">
-      <t>ヒキスウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ジッソウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>使用可能なファイルを正規表現で定義（.csv）</t>
     <rPh sb="0" eb="4">
       <t>シヨウカノウ</t>
@@ -1338,6 +1188,13 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>par2定義</t>
+    <rPh sb="4" eb="6">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>←</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1370,6 +1227,107 @@
     <rPh sb="6" eb="7">
       <t>オオ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エラーメッセージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パラメータ3個以上</t>
+    <rPh sb="6" eb="7">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第2パラメータが無い</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第2パラメータがない</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>存在しないパラメータ</t>
+    <rPh sb="0" eb="2">
+      <t>ソンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘルプメッセージ関数定義</t>
+    <rPh sb="8" eb="10">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘルプメッセージ定義</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mode選択のパラメータエラー</t>
+    <rPh sb="4" eb="6">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>引数がゼロ、もしくは規定より多いこと。</t>
+    <rPh sb="0" eb="2">
+      <t>ヒキスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第1引数が-h</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒキスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘルプメッセージを表示</t>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘルプメッセージ関数</t>
+    <rPh sb="8" eb="10">
+      <t>カンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘルプメッセージを表示する</t>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第一引数がどれでもなければエラー表示</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1377,7 +1335,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1421,13 +1379,27 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1444,7 +1416,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1463,7 +1435,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1481,71 +1456,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>171449</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>161924</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>295274</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>142874</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="乗算記号 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBC7B6D8-1EF4-22A9-1F9C-E41E5352EE82}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1142999" y="5162549"/>
-          <a:ext cx="4238625" cy="2600325"/>
-        </a:xfrm>
-        <a:prstGeom prst="mathMultiply">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1865,10 +1775,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBAE3C68-FE4B-486D-B1C9-A0DA74E03356}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.4">
@@ -1918,7 +1829,7 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
@@ -1926,13 +1837,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
@@ -1945,600 +1856,635 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="D11" t="s">
-        <v>13</v>
+        <v>139</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11" t="s">
-        <v>27</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="s">
+        <v>136</v>
+      </c>
+      <c r="H12" t="s">
         <v>23</v>
-      </c>
-      <c r="F12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="D13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>28</v>
+        <v>136</v>
       </c>
       <c r="H13" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="D14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>136</v>
       </c>
       <c r="H14" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B16" s="1" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.4">
       <c r="D17" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="F17" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.4">
       <c r="D18" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="F18" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.4">
       <c r="D19" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F19" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.4">
       <c r="D20" t="s">
-        <v>119</v>
-      </c>
-      <c r="F20" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.4">
       <c r="D21" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="D22" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B24" t="s">
-        <v>110</v>
+        <v>104</v>
+      </c>
+      <c r="D24" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B25" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B28" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B29" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B30" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B31" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D33" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D34" s="5" t="s">
-        <v>123</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="D25" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B26" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D35" s="4"/>
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D36" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F096B9D8-F958-4268-B6BD-A20FCF680D12}">
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B16" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B17" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B18" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B19" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" t="s">
+        <v>116</v>
+      </c>
+      <c r="F21" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" t="s">
+        <v>116</v>
+      </c>
+      <c r="F22" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" t="s">
+        <v>117</v>
+      </c>
+      <c r="F23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="C27" t="s">
+        <v>131</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>144</v>
+      </c>
+      <c r="I27" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B28" t="s">
+        <v>123</v>
+      </c>
+      <c r="I28" t="s">
+        <v>122</v>
+      </c>
+      <c r="M28" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B29" t="s">
+        <v>20</v>
+      </c>
+      <c r="I29" t="s">
+        <v>20</v>
+      </c>
+      <c r="M29" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B30" t="s">
+        <v>124</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30" t="s">
+        <v>125</v>
+      </c>
+      <c r="M30" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B31" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31">
+        <v>2</v>
+      </c>
+      <c r="I31" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A32">
+        <v>1</v>
+      </c>
+      <c r="B32" t="s">
+        <v>29</v>
+      </c>
+      <c r="H32">
+        <v>3</v>
+      </c>
+      <c r="I32" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A33">
+        <v>2</v>
+      </c>
+      <c r="B33" t="s">
+        <v>28</v>
+      </c>
+      <c r="I33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A34">
+        <v>3</v>
+      </c>
+      <c r="B34" t="s">
+        <v>30</v>
+      </c>
+      <c r="I34" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B35" t="s">
+        <v>20</v>
+      </c>
+      <c r="I35" t="s">
+        <v>20</v>
+      </c>
+      <c r="M35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B36" t="s">
+        <v>128</v>
+      </c>
+      <c r="F36" t="s">
+        <v>132</v>
+      </c>
+      <c r="M36" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>147</v>
+      </c>
+      <c r="D41" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>26</v>
+      </c>
+      <c r="B43" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B44" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B45" s="1"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>42</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47" t="s">
+        <v>38</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="D48">
+        <v>2</v>
+      </c>
+      <c r="E48" t="s">
+        <v>43</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="D49">
+        <v>3</v>
+      </c>
+      <c r="E49" t="s">
+        <v>44</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="D50">
+        <v>4</v>
+      </c>
+      <c r="E50" t="s">
+        <v>45</v>
+      </c>
+      <c r="H50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="D51">
+        <v>5</v>
+      </c>
+      <c r="E51" t="s">
+        <v>57</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="E52" t="s">
+        <v>58</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="N52" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>59</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="C55">
+        <v>2</v>
+      </c>
+      <c r="D55" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="C56">
+        <v>3</v>
+      </c>
+      <c r="D56" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="C59">
+        <v>2</v>
+      </c>
+      <c r="D59" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="C60">
+        <v>3</v>
+      </c>
+      <c r="D60" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="C61">
+        <v>4</v>
+      </c>
+      <c r="D61" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="C62">
+        <v>5</v>
+      </c>
+      <c r="D62" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="D63" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A65" t="s">
+        <v>37</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" s="6" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B13" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B14" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B15" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" t="s">
-        <v>134</v>
-      </c>
-      <c r="F16" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" t="s">
-        <v>134</v>
-      </c>
-      <c r="F17" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" t="s">
-        <v>134</v>
-      </c>
-      <c r="F18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A19" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="E19" t="s">
-        <v>135</v>
-      </c>
-      <c r="F19" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="C23" t="s">
-        <v>148</v>
-      </c>
-      <c r="D23">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C66">
+        <v>2</v>
+      </c>
+      <c r="D66" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="D67" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A70" t="s">
+        <v>110</v>
+      </c>
+      <c r="C70">
         <v>1</v>
       </c>
-      <c r="E23" t="s">
-        <v>43</v>
-      </c>
-      <c r="H23" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B24" t="s">
-        <v>141</v>
-      </c>
-      <c r="I24" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B26" t="s">
-        <v>142</v>
-      </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-      <c r="I26" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B27" t="s">
-        <v>21</v>
-      </c>
-      <c r="H27">
+      <c r="D70" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C71">
         <v>2</v>
       </c>
-      <c r="I27" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A28">
-        <v>1</v>
-      </c>
-      <c r="B28" t="s">
-        <v>35</v>
-      </c>
-      <c r="H28">
+      <c r="D71" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C72">
         <v>3</v>
       </c>
-      <c r="I28" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A29">
-        <v>2</v>
-      </c>
-      <c r="B29" t="s">
-        <v>34</v>
-      </c>
-      <c r="I29" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A30">
-        <v>3</v>
-      </c>
-      <c r="B30" t="s">
-        <v>36</v>
-      </c>
-      <c r="I30" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B31" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B32" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A36" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A37" t="s">
-        <v>32</v>
-      </c>
-      <c r="B37" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="B38" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="B39" s="1"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A41" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41">
-        <v>1</v>
-      </c>
-      <c r="E41" t="s">
-        <v>45</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="D42">
-        <v>2</v>
-      </c>
-      <c r="E42" t="s">
-        <v>50</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="D43">
-        <v>3</v>
-      </c>
-      <c r="E43" t="s">
-        <v>51</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="D44">
+      <c r="D72" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C73">
         <v>4</v>
       </c>
-      <c r="E44" t="s">
-        <v>52</v>
-      </c>
-      <c r="H44" t="s">
-        <v>59</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="D45">
-        <v>5</v>
-      </c>
-      <c r="E45" t="s">
-        <v>64</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="E46" t="s">
-        <v>65</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="N46" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A48" t="s">
-        <v>66</v>
-      </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-      <c r="D48" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C49">
-        <v>2</v>
-      </c>
-      <c r="D49" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C50">
-        <v>3</v>
-      </c>
-      <c r="D50" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A52" t="s">
-        <v>63</v>
-      </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="D52" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C53">
-        <v>2</v>
-      </c>
-      <c r="D53" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C54">
-        <v>3</v>
-      </c>
-      <c r="D54" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C55">
-        <v>4</v>
-      </c>
-      <c r="D55" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C56">
-        <v>5</v>
-      </c>
-      <c r="D56" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="D57" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A59" t="s">
-        <v>44</v>
-      </c>
-      <c r="C59">
-        <v>1</v>
-      </c>
-      <c r="D59" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C60">
-        <v>2</v>
-      </c>
-      <c r="D60" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="D61" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A64" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C64">
-        <v>1</v>
-      </c>
-      <c r="D64" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.4">
-      <c r="C65">
-        <v>2</v>
-      </c>
-      <c r="D65" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.4">
-      <c r="C66">
-        <v>3</v>
-      </c>
-      <c r="D66" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="67" spans="3:4" x14ac:dyDescent="0.4">
-      <c r="C67">
-        <v>4</v>
-      </c>
-      <c r="D67" t="s">
-        <v>131</v>
+      <c r="D73" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2559,115 +2505,115 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" t="s">
         <v>81</v>
-      </c>
-      <c r="D1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" t="s">
         <v>76</v>
-      </c>
-      <c r="C4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="D11" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="D12" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="D13" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="D14" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
